--- a/PD Course Planner Template.xlsx
+++ b/PD Course Planner Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hariharan_chipedge\Music\engg-automation-git-file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3EA04F-8909-40C7-A30B-86E7C493BD67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD86401E-94DD-4358-A17E-5CB54A3D4C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="135">
   <si>
     <t>Assessments / Soft Skills Session : Fridays</t>
   </si>
@@ -378,9 +378,6 @@
 Technical Presentaion Session </t>
   </si>
   <si>
-    <t>Ganesh Chathurdhi Holiday</t>
-  </si>
-  <si>
     <t>Python</t>
   </si>
   <si>
@@ -394,9 +391,6 @@
   </si>
   <si>
     <t>Project Execution Time</t>
-  </si>
-  <si>
-    <t>Mahatma Gandhi Jayanthi-Holiday</t>
   </si>
   <si>
     <t>Project Submission Deadline</t>
@@ -457,7 +451,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dddd\,\ d\ mmmm\,\ yyyy"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -556,13 +550,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Verdana"/>
@@ -591,7 +578,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -620,12 +607,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FFC9DAF8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -925,7 +906,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1004,191 +985,190 @@
     <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1425,55 +1405,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="88" t="s">
-        <v>128</v>
-      </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="76"/>
+      <c r="A1" s="98" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="62"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
     <row r="2" spans="1:12" ht="91.8" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="91" t="s">
+      <c r="A2" s="106" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="B2" s="75"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="115" t="s">
-        <v>136</v>
-      </c>
       <c r="E2" s="33"/>
-      <c r="F2" s="116" t="s">
-        <v>130</v>
-      </c>
-      <c r="G2" s="117"/>
-      <c r="H2" s="108" t="s">
-        <v>129</v>
-      </c>
-      <c r="I2" s="109"/>
+      <c r="F2" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="G2" s="59"/>
+      <c r="H2" s="56" t="s">
+        <v>127</v>
+      </c>
+      <c r="I2" s="57"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="76"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
       <c r="D3" s="33"/>
       <c r="E3" s="33"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="76"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="62"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -1485,37 +1465,37 @@
       <c r="B4" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="82" t="s">
+      <c r="C4" s="100" t="s">
+        <v>129</v>
+      </c>
+      <c r="D4" s="55"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="100" t="s">
+        <v>130</v>
+      </c>
+      <c r="G4" s="55"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="41" t="s">
         <v>131</v>
-      </c>
-      <c r="D4" s="49"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="82" t="s">
-        <v>132</v>
-      </c>
-      <c r="G4" s="49"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="42" t="s">
-        <v>133</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="102">
+      <c r="A5" s="80">
         <v>1</v>
       </c>
-      <c r="B5" s="62" t="s">
+      <c r="B5" s="110" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="46"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -1523,10 +1503,10 @@
     <row r="6" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="51"/>
       <c r="B6" s="3"/>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="44"/>
+      <c r="D6" s="45"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
@@ -1539,20 +1519,20 @@
     <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="51"/>
       <c r="B7" s="3"/>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="111" t="s">
         <v>5</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="90"/>
-      <c r="F7" s="43" t="s">
+      <c r="E7" s="83"/>
+      <c r="F7" s="44" t="s">
         <v>7</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="50"/>
+      <c r="H7" s="78"/>
       <c r="I7" s="8" t="s">
         <v>9</v>
       </c>
@@ -1563,16 +1543,16 @@
     <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="51"/>
       <c r="B8" s="3"/>
-      <c r="C8" s="59"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="6" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="51"/>
-      <c r="F8" s="52"/>
+      <c r="F8" s="65"/>
       <c r="G8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="52"/>
+      <c r="H8" s="65"/>
       <c r="I8" s="8" t="s">
         <v>9</v>
       </c>
@@ -1583,7 +1563,7 @@
     <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="51"/>
       <c r="B9" s="3"/>
-      <c r="C9" s="67"/>
+      <c r="C9" s="54"/>
       <c r="D9" s="23" t="s">
         <v>12</v>
       </c>
@@ -1598,78 +1578,78 @@
       <c r="I9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="101"/>
+      <c r="J9" s="85"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="51"/>
       <c r="B10" s="3"/>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="45"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="43" t="s">
+      <c r="D10" s="46"/>
+      <c r="E10" s="107"/>
+      <c r="F10" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="60"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="70"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="51"/>
       <c r="B11" s="3"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="60"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="70"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="52"/>
-      <c r="B12" s="53" t="s">
+      <c r="A12" s="65"/>
+      <c r="B12" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="46"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="63">
+      <c r="A13" s="50">
         <v>2</v>
       </c>
       <c r="B13" s="35"/>
-      <c r="C13" s="83" t="s">
+      <c r="C13" s="97" t="s">
         <v>5</v>
       </c>
       <c r="D13" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="50"/>
-      <c r="F13" s="96" t="s">
+      <c r="E13" s="78"/>
+      <c r="F13" s="95" t="s">
         <v>18</v>
       </c>
       <c r="G13" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="50"/>
-      <c r="I13" s="71" t="s">
+      <c r="H13" s="78"/>
+      <c r="I13" s="66" t="s">
         <v>20</v>
       </c>
       <c r="J13" s="2"/>
@@ -1679,12 +1659,12 @@
     <row r="14" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="51"/>
       <c r="B14" s="35"/>
-      <c r="C14" s="84"/>
+      <c r="C14" s="92"/>
       <c r="D14" s="36" t="s">
         <v>21</v>
       </c>
       <c r="E14" s="51"/>
-      <c r="F14" s="84"/>
+      <c r="F14" s="92"/>
       <c r="G14" s="36" t="s">
         <v>22</v>
       </c>
@@ -1697,12 +1677,12 @@
     <row r="15" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="51"/>
       <c r="B15" s="35"/>
-      <c r="C15" s="84"/>
+      <c r="C15" s="92"/>
       <c r="D15" s="36" t="s">
         <v>21</v>
       </c>
       <c r="E15" s="51"/>
-      <c r="F15" s="85"/>
+      <c r="F15" s="93"/>
       <c r="G15" s="36" t="s">
         <v>22</v>
       </c>
@@ -1715,17 +1695,17 @@
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="51"/>
       <c r="B16" s="35"/>
-      <c r="C16" s="85"/>
-      <c r="D16" s="39" t="s">
+      <c r="C16" s="93"/>
+      <c r="D16" s="38" t="s">
         <v>23</v>
       </c>
       <c r="E16" s="51"/>
-      <c r="F16" s="48" t="s">
+      <c r="F16" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="52"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="65"/>
+      <c r="I16" s="65"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
@@ -1733,17 +1713,17 @@
     <row r="17" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="51"/>
       <c r="B17" s="3"/>
-      <c r="C17" s="72" t="s">
+      <c r="C17" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="49"/>
+      <c r="D17" s="55"/>
       <c r="E17" s="51"/>
-      <c r="F17" s="43" t="s">
+      <c r="F17" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="55"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="53"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
@@ -1751,53 +1731,53 @@
     <row r="18" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="51"/>
       <c r="B18" s="3"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="67"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="55"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="51"/>
-      <c r="B19" s="53" t="s">
+      <c r="B19" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="45"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="46"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="63">
+      <c r="A20" s="50">
         <v>3</v>
       </c>
       <c r="B20" s="35"/>
-      <c r="C20" s="94" t="s">
+      <c r="C20" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="41" t="s">
+      <c r="D20" s="40" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="23"/>
-      <c r="F20" s="83" t="s">
+      <c r="F20" s="97" t="s">
         <v>18</v>
       </c>
       <c r="G20" s="34" t="s">
         <v>26</v>
       </c>
       <c r="H20" s="23"/>
-      <c r="I20" s="111" t="s">
+      <c r="I20" s="63" t="s">
         <v>20</v>
       </c>
       <c r="J20" s="2"/>
@@ -1807,17 +1787,17 @@
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="51"/>
       <c r="B21" s="35"/>
-      <c r="C21" s="84"/>
-      <c r="D21" s="40" t="s">
+      <c r="C21" s="92"/>
+      <c r="D21" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="64"/>
-      <c r="F21" s="84"/>
-      <c r="G21" s="40" t="s">
+      <c r="E21" s="107"/>
+      <c r="F21" s="92"/>
+      <c r="G21" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="H21" s="50"/>
-      <c r="I21" s="61"/>
+      <c r="H21" s="78"/>
+      <c r="I21" s="64"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
@@ -1825,17 +1805,17 @@
     <row r="22" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="51"/>
       <c r="B22" s="35"/>
-      <c r="C22" s="84"/>
+      <c r="C22" s="92"/>
       <c r="D22" s="36" t="s">
         <v>29</v>
       </c>
       <c r="E22" s="51"/>
-      <c r="F22" s="84"/>
+      <c r="F22" s="92"/>
       <c r="G22" s="36" t="s">
         <v>30</v>
       </c>
       <c r="H22" s="51"/>
-      <c r="I22" s="61"/>
+      <c r="I22" s="64"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
@@ -1843,17 +1823,17 @@
     <row r="23" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="51"/>
       <c r="B23" s="35"/>
-      <c r="C23" s="85"/>
+      <c r="C23" s="93"/>
       <c r="D23" s="36" t="s">
         <v>31</v>
       </c>
       <c r="E23" s="51"/>
-      <c r="F23" s="85"/>
+      <c r="F23" s="93"/>
       <c r="G23" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="52"/>
-      <c r="I23" s="49"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="55"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
@@ -1861,17 +1841,17 @@
     <row r="24" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="51"/>
       <c r="B24" s="3"/>
-      <c r="C24" s="72" t="s">
+      <c r="C24" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="D24" s="49"/>
+      <c r="D24" s="55"/>
       <c r="E24" s="51"/>
-      <c r="F24" s="95" t="s">
+      <c r="F24" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="G24" s="60"/>
-      <c r="H24" s="60"/>
-      <c r="I24" s="61"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="64"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
@@ -1879,53 +1859,53 @@
     <row r="25" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="51"/>
       <c r="B25" s="3"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="52"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="55"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="51"/>
-      <c r="B26" s="53" t="s">
+      <c r="B26" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="45"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="46"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="63">
+      <c r="A27" s="50">
         <v>4</v>
       </c>
       <c r="B27" s="3"/>
-      <c r="C27" s="47" t="s">
+      <c r="C27" s="49" t="s">
         <v>5</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E27" s="50"/>
-      <c r="F27" s="47" t="s">
+      <c r="E27" s="78"/>
+      <c r="F27" s="49" t="s">
         <v>18</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="H27" s="50"/>
-      <c r="I27" s="71" t="s">
+      <c r="H27" s="78"/>
+      <c r="I27" s="66" t="s">
         <v>20</v>
       </c>
       <c r="J27" s="2"/>
@@ -1971,17 +1951,17 @@
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="51"/>
       <c r="B30" s="3"/>
-      <c r="C30" s="52"/>
+      <c r="C30" s="65"/>
       <c r="D30" s="6" t="s">
         <v>39</v>
       </c>
       <c r="E30" s="51"/>
-      <c r="F30" s="52"/>
+      <c r="F30" s="65"/>
       <c r="G30" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H30" s="51"/>
-      <c r="I30" s="52"/>
+      <c r="I30" s="65"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
@@ -1989,17 +1969,17 @@
     <row r="31" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="51"/>
       <c r="B31" s="3"/>
-      <c r="C31" s="47" t="s">
+      <c r="C31" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="45"/>
+      <c r="D31" s="46"/>
       <c r="E31" s="51"/>
-      <c r="F31" s="66" t="s">
+      <c r="F31" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="G31" s="55"/>
+      <c r="G31" s="53"/>
       <c r="H31" s="51"/>
-      <c r="I31" s="71" t="s">
+      <c r="I31" s="66" t="s">
         <v>42</v>
       </c>
       <c r="J31" s="2"/>
@@ -2009,13 +1989,13 @@
     <row r="32" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="51"/>
       <c r="B32" s="3"/>
-      <c r="C32" s="47"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="67"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
+      <c r="C32" s="49"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="65"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="65"/>
+      <c r="I32" s="65"/>
       <c r="J32" s="12" t="s">
         <v>43</v>
       </c>
@@ -2024,40 +2004,40 @@
     </row>
     <row r="33" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="51"/>
-      <c r="B33" s="53" t="s">
+      <c r="B33" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="44"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
-      <c r="H33" s="44"/>
-      <c r="I33" s="45"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="46"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="63">
+      <c r="A34" s="50">
         <v>5</v>
       </c>
       <c r="B34" s="3"/>
-      <c r="C34" s="47" t="s">
+      <c r="C34" s="49" t="s">
         <v>5</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E34" s="50"/>
-      <c r="F34" s="47" t="s">
+      <c r="E34" s="78"/>
+      <c r="F34" s="49" t="s">
         <v>18</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="H34" s="50"/>
-      <c r="I34" s="71" t="s">
+      <c r="H34" s="78"/>
+      <c r="I34" s="66" t="s">
         <v>20</v>
       </c>
       <c r="J34" s="2"/>
@@ -2103,17 +2083,17 @@
     <row r="37" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="51"/>
       <c r="B37" s="3"/>
-      <c r="C37" s="52"/>
+      <c r="C37" s="65"/>
       <c r="D37" s="13" t="s">
         <v>48</v>
       </c>
       <c r="E37" s="51"/>
-      <c r="F37" s="52"/>
+      <c r="F37" s="65"/>
       <c r="G37" s="6" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="51"/>
-      <c r="I37" s="52"/>
+      <c r="I37" s="65"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
@@ -2121,17 +2101,17 @@
     <row r="38" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="51"/>
       <c r="B38" s="3"/>
-      <c r="C38" s="47" t="s">
+      <c r="C38" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="D38" s="45"/>
+      <c r="D38" s="46"/>
       <c r="E38" s="51"/>
-      <c r="F38" s="77" t="s">
+      <c r="F38" s="108" t="s">
         <v>49</v>
       </c>
-      <c r="G38" s="55"/>
+      <c r="G38" s="53"/>
       <c r="H38" s="51"/>
-      <c r="I38" s="71" t="s">
+      <c r="I38" s="66" t="s">
         <v>42</v>
       </c>
       <c r="J38" s="2"/>
@@ -2141,35 +2121,35 @@
     <row r="39" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="51"/>
       <c r="B39" s="3"/>
-      <c r="C39" s="47"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="49"/>
-      <c r="H39" s="52"/>
-      <c r="I39" s="52"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="65"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="65"/>
+      <c r="I39" s="65"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
     </row>
     <row r="40" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="51"/>
-      <c r="B40" s="53" t="s">
+      <c r="B40" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C40" s="44"/>
-      <c r="D40" s="44"/>
-      <c r="E40" s="44"/>
-      <c r="F40" s="44"/>
-      <c r="G40" s="44"/>
-      <c r="H40" s="44"/>
-      <c r="I40" s="45"/>
+      <c r="C40" s="45"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="45"/>
+      <c r="I40" s="46"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="63">
+      <c r="A41" s="50">
         <v>6</v>
       </c>
       <c r="B41" s="3"/>
@@ -2179,13 +2159,13 @@
       <c r="D41" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="E41" s="50"/>
+      <c r="E41" s="78"/>
       <c r="F41" s="13"/>
       <c r="G41" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H41" s="50"/>
-      <c r="I41" s="71" t="s">
+      <c r="H41" s="78"/>
+      <c r="I41" s="66" t="s">
         <v>20</v>
       </c>
       <c r="J41" s="2"/>
@@ -2207,7 +2187,7 @@
         <v>54</v>
       </c>
       <c r="H42" s="51"/>
-      <c r="I42" s="52"/>
+      <c r="I42" s="65"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
@@ -2222,12 +2202,12 @@
         <v>56</v>
       </c>
       <c r="E43" s="51"/>
-      <c r="F43" s="47" t="s">
+      <c r="F43" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="G43" s="45"/>
+      <c r="G43" s="46"/>
       <c r="H43" s="51"/>
-      <c r="I43" s="71" t="s">
+      <c r="I43" s="66" t="s">
         <v>57</v>
       </c>
       <c r="J43" s="2"/>
@@ -2244,12 +2224,12 @@
         <v>59</v>
       </c>
       <c r="E44" s="51"/>
-      <c r="F44" s="47" t="s">
+      <c r="F44" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="G44" s="45"/>
+      <c r="G44" s="46"/>
       <c r="H44" s="51"/>
-      <c r="I44" s="52"/>
+      <c r="I44" s="65"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
@@ -2257,17 +2237,17 @@
     <row r="45" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="51"/>
       <c r="B45" s="3"/>
-      <c r="C45" s="112" t="s">
+      <c r="C45" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="D45" s="55"/>
+      <c r="D45" s="53"/>
       <c r="E45" s="51"/>
-      <c r="F45" s="89" t="s">
+      <c r="F45" s="99" t="s">
         <v>60</v>
       </c>
-      <c r="G45" s="55"/>
+      <c r="G45" s="53"/>
       <c r="H45" s="51"/>
-      <c r="I45" s="71"/>
+      <c r="I45" s="66"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
@@ -2275,51 +2255,51 @@
     <row r="46" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="51"/>
       <c r="B46" s="3"/>
-      <c r="C46" s="67"/>
-      <c r="D46" s="49"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="49"/>
-      <c r="H46" s="52"/>
-      <c r="I46" s="52"/>
+      <c r="C46" s="54"/>
+      <c r="D46" s="55"/>
+      <c r="E46" s="65"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="55"/>
+      <c r="H46" s="65"/>
+      <c r="I46" s="65"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
     </row>
     <row r="47" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="51"/>
-      <c r="B47" s="53" t="s">
+      <c r="B47" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C47" s="44"/>
-      <c r="D47" s="44"/>
-      <c r="E47" s="44"/>
-      <c r="F47" s="44"/>
-      <c r="G47" s="44"/>
-      <c r="H47" s="44"/>
-      <c r="I47" s="45"/>
+      <c r="C47" s="45"/>
+      <c r="D47" s="45"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="45"/>
+      <c r="G47" s="45"/>
+      <c r="H47" s="45"/>
+      <c r="I47" s="46"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="63">
+      <c r="A48" s="50">
         <v>7</v>
       </c>
       <c r="B48" s="3"/>
-      <c r="C48" s="47" t="s">
+      <c r="C48" s="49" t="s">
         <v>58</v>
       </c>
       <c r="D48" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E48" s="50"/>
-      <c r="F48" s="47" t="s">
+      <c r="E48" s="78"/>
+      <c r="F48" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="G48" s="45"/>
-      <c r="H48" s="50"/>
-      <c r="I48" s="71" t="s">
+      <c r="G48" s="46"/>
+      <c r="H48" s="78"/>
+      <c r="I48" s="66" t="s">
         <v>57</v>
       </c>
       <c r="J48" s="2"/>
@@ -2334,10 +2314,10 @@
         <v>62</v>
       </c>
       <c r="E49" s="51"/>
-      <c r="F49" s="47" t="s">
+      <c r="F49" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="G49" s="45"/>
+      <c r="G49" s="46"/>
       <c r="H49" s="51"/>
       <c r="I49" s="51"/>
       <c r="J49" s="2"/>
@@ -2352,10 +2332,10 @@
         <v>63</v>
       </c>
       <c r="E50" s="51"/>
-      <c r="F50" s="73" t="s">
+      <c r="F50" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="G50" s="45"/>
+      <c r="G50" s="46"/>
       <c r="H50" s="51"/>
       <c r="I50" s="51"/>
       <c r="J50" s="2"/>
@@ -2365,17 +2345,17 @@
     <row r="51" spans="1:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="51"/>
       <c r="B51" s="3"/>
-      <c r="C51" s="52"/>
+      <c r="C51" s="65"/>
       <c r="D51" s="6" t="s">
         <v>64</v>
       </c>
       <c r="E51" s="51"/>
-      <c r="F51" s="73" t="s">
+      <c r="F51" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="G51" s="45"/>
+      <c r="G51" s="46"/>
       <c r="H51" s="51"/>
-      <c r="I51" s="52"/>
+      <c r="I51" s="65"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
@@ -2383,17 +2363,17 @@
     <row r="52" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="51"/>
       <c r="B52" s="3"/>
-      <c r="C52" s="47" t="s">
+      <c r="C52" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="D52" s="45"/>
+      <c r="D52" s="46"/>
       <c r="E52" s="51"/>
-      <c r="F52" s="66" t="s">
+      <c r="F52" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="G52" s="55"/>
+      <c r="G52" s="53"/>
       <c r="H52" s="51"/>
-      <c r="I52" s="71" t="s">
+      <c r="I52" s="66" t="s">
         <v>42</v>
       </c>
       <c r="J52" s="2"/>
@@ -2403,51 +2383,51 @@
     <row r="53" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="51"/>
       <c r="B53" s="3"/>
-      <c r="C53" s="47"/>
-      <c r="D53" s="45"/>
-      <c r="E53" s="52"/>
-      <c r="F53" s="67"/>
-      <c r="G53" s="49"/>
-      <c r="H53" s="52"/>
-      <c r="I53" s="52"/>
+      <c r="C53" s="49"/>
+      <c r="D53" s="46"/>
+      <c r="E53" s="65"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="55"/>
+      <c r="H53" s="65"/>
+      <c r="I53" s="65"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
     </row>
     <row r="54" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="51"/>
-      <c r="B54" s="53" t="s">
+      <c r="B54" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C54" s="44"/>
-      <c r="D54" s="44"/>
-      <c r="E54" s="44"/>
-      <c r="F54" s="44"/>
-      <c r="G54" s="44"/>
-      <c r="H54" s="44"/>
-      <c r="I54" s="45"/>
+      <c r="C54" s="45"/>
+      <c r="D54" s="45"/>
+      <c r="E54" s="45"/>
+      <c r="F54" s="45"/>
+      <c r="G54" s="45"/>
+      <c r="H54" s="45"/>
+      <c r="I54" s="46"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="63">
+      <c r="A55" s="50">
         <v>8</v>
       </c>
       <c r="B55" s="3"/>
-      <c r="C55" s="47" t="s">
+      <c r="C55" s="49" t="s">
         <v>58</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E55" s="50"/>
-      <c r="F55" s="73" t="s">
+      <c r="E55" s="78"/>
+      <c r="F55" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="G55" s="45"/>
-      <c r="H55" s="50"/>
-      <c r="I55" s="98" t="s">
+      <c r="G55" s="46"/>
+      <c r="H55" s="78"/>
+      <c r="I55" s="73" t="s">
         <v>57</v>
       </c>
       <c r="J55" s="2"/>
@@ -2462,10 +2442,10 @@
         <v>67</v>
       </c>
       <c r="E56" s="51"/>
-      <c r="F56" s="73" t="s">
+      <c r="F56" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="G56" s="45"/>
+      <c r="G56" s="46"/>
       <c r="H56" s="51"/>
       <c r="I56" s="51"/>
       <c r="J56" s="2"/>
@@ -2475,15 +2455,15 @@
     <row r="57" spans="1:12" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="51"/>
       <c r="B57" s="3"/>
-      <c r="C57" s="52"/>
+      <c r="C57" s="65"/>
       <c r="D57" s="13" t="s">
         <v>68</v>
       </c>
       <c r="E57" s="51"/>
-      <c r="F57" s="47" t="s">
+      <c r="F57" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="G57" s="45"/>
+      <c r="G57" s="46"/>
       <c r="H57" s="51"/>
       <c r="I57" s="51"/>
       <c r="J57" s="2"/>
@@ -2500,10 +2480,10 @@
         <v>56</v>
       </c>
       <c r="E58" s="51"/>
-      <c r="F58" s="47" t="s">
+      <c r="F58" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="G58" s="45"/>
+      <c r="G58" s="46"/>
       <c r="H58" s="51"/>
       <c r="I58" s="51"/>
       <c r="J58" s="2"/>
@@ -2513,17 +2493,17 @@
     <row r="59" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="51"/>
       <c r="B59" s="3"/>
-      <c r="C59" s="47" t="s">
+      <c r="C59" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="D59" s="45"/>
+      <c r="D59" s="46"/>
       <c r="E59" s="51"/>
-      <c r="F59" s="77" t="s">
+      <c r="F59" s="108" t="s">
         <v>69</v>
       </c>
-      <c r="G59" s="55"/>
+      <c r="G59" s="53"/>
       <c r="H59" s="51"/>
-      <c r="I59" s="71" t="s">
+      <c r="I59" s="66" t="s">
         <v>42</v>
       </c>
       <c r="J59" s="2"/>
@@ -2533,35 +2513,35 @@
     <row r="60" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="51"/>
       <c r="B60" s="3"/>
-      <c r="C60" s="47"/>
-      <c r="D60" s="45"/>
-      <c r="E60" s="52"/>
-      <c r="F60" s="67"/>
-      <c r="G60" s="49"/>
-      <c r="H60" s="52"/>
-      <c r="I60" s="52"/>
+      <c r="C60" s="49"/>
+      <c r="D60" s="46"/>
+      <c r="E60" s="65"/>
+      <c r="F60" s="54"/>
+      <c r="G60" s="55"/>
+      <c r="H60" s="65"/>
+      <c r="I60" s="65"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="51"/>
-      <c r="B61" s="53" t="s">
+      <c r="B61" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C61" s="44"/>
-      <c r="D61" s="44"/>
-      <c r="E61" s="44"/>
-      <c r="F61" s="44"/>
-      <c r="G61" s="44"/>
-      <c r="H61" s="44"/>
-      <c r="I61" s="45"/>
+      <c r="C61" s="45"/>
+      <c r="D61" s="45"/>
+      <c r="E61" s="45"/>
+      <c r="F61" s="45"/>
+      <c r="G61" s="45"/>
+      <c r="H61" s="45"/>
+      <c r="I61" s="46"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
     </row>
     <row r="62" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="63">
+      <c r="A62" s="50">
         <v>9</v>
       </c>
       <c r="B62" s="3"/>
@@ -2571,13 +2551,13 @@
       <c r="D62" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="E62" s="50"/>
-      <c r="F62" s="47" t="s">
+      <c r="E62" s="78"/>
+      <c r="F62" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="G62" s="45"/>
-      <c r="H62" s="50"/>
-      <c r="I62" s="71" t="s">
+      <c r="G62" s="46"/>
+      <c r="H62" s="78"/>
+      <c r="I62" s="66" t="s">
         <v>57</v>
       </c>
       <c r="J62" s="2"/>
@@ -2594,10 +2574,10 @@
         <v>71</v>
       </c>
       <c r="E63" s="51"/>
-      <c r="F63" s="47" t="s">
+      <c r="F63" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="G63" s="45"/>
+      <c r="G63" s="46"/>
       <c r="H63" s="51"/>
       <c r="I63" s="51"/>
       <c r="J63" s="2"/>
@@ -2614,10 +2594,10 @@
         <v>71</v>
       </c>
       <c r="E64" s="51"/>
-      <c r="F64" s="47" t="s">
+      <c r="F64" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="G64" s="45"/>
+      <c r="G64" s="46"/>
       <c r="H64" s="51"/>
       <c r="I64" s="51"/>
       <c r="J64" s="2"/>
@@ -2634,12 +2614,12 @@
         <v>71</v>
       </c>
       <c r="E65" s="51"/>
-      <c r="F65" s="47" t="s">
+      <c r="F65" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="G65" s="45"/>
+      <c r="G65" s="46"/>
       <c r="H65" s="51"/>
-      <c r="I65" s="52"/>
+      <c r="I65" s="65"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
@@ -2647,17 +2627,17 @@
     <row r="66" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="51"/>
       <c r="B66" s="3"/>
-      <c r="C66" s="65" t="s">
+      <c r="C66" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="D66" s="45"/>
+      <c r="D66" s="46"/>
       <c r="E66" s="51"/>
-      <c r="F66" s="66" t="s">
+      <c r="F66" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="G66" s="55"/>
+      <c r="G66" s="53"/>
       <c r="H66" s="51"/>
-      <c r="I66" s="71" t="s">
+      <c r="I66" s="66" t="s">
         <v>42</v>
       </c>
       <c r="J66" s="12" t="s">
@@ -2669,51 +2649,51 @@
     <row r="67" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="51"/>
       <c r="B67" s="3"/>
-      <c r="C67" s="65"/>
-      <c r="D67" s="45"/>
-      <c r="E67" s="52"/>
-      <c r="F67" s="67"/>
-      <c r="G67" s="49"/>
-      <c r="H67" s="52"/>
-      <c r="I67" s="52"/>
+      <c r="C67" s="89"/>
+      <c r="D67" s="46"/>
+      <c r="E67" s="65"/>
+      <c r="F67" s="54"/>
+      <c r="G67" s="55"/>
+      <c r="H67" s="65"/>
+      <c r="I67" s="65"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
     </row>
     <row r="68" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="51"/>
-      <c r="B68" s="53" t="s">
+      <c r="B68" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C68" s="44"/>
-      <c r="D68" s="44"/>
-      <c r="E68" s="44"/>
-      <c r="F68" s="44"/>
-      <c r="G68" s="44"/>
-      <c r="H68" s="44"/>
-      <c r="I68" s="45"/>
+      <c r="C68" s="45"/>
+      <c r="D68" s="45"/>
+      <c r="E68" s="45"/>
+      <c r="F68" s="45"/>
+      <c r="G68" s="45"/>
+      <c r="H68" s="45"/>
+      <c r="I68" s="46"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
     </row>
     <row r="69" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="63">
+      <c r="A69" s="50">
         <v>10</v>
       </c>
       <c r="B69" s="3"/>
-      <c r="C69" s="107" t="s">
+      <c r="C69" s="47" t="s">
         <v>74</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>74</v>
       </c>
       <c r="E69" s="7"/>
-      <c r="F69" s="47" t="s">
+      <c r="F69" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="G69" s="45"/>
+      <c r="G69" s="46"/>
       <c r="H69" s="7"/>
-      <c r="I69" s="100" t="s">
+      <c r="I69" s="90" t="s">
         <v>75</v>
       </c>
       <c r="J69" s="2"/>
@@ -2723,17 +2703,17 @@
     <row r="70" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="51"/>
       <c r="B70" s="3"/>
-      <c r="C70" s="59"/>
+      <c r="C70" s="48"/>
       <c r="D70" s="13" t="s">
         <v>74</v>
       </c>
       <c r="E70" s="11"/>
-      <c r="F70" s="47" t="s">
+      <c r="F70" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="G70" s="45"/>
+      <c r="G70" s="46"/>
       <c r="H70" s="11"/>
-      <c r="I70" s="61"/>
+      <c r="I70" s="64"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
@@ -2741,17 +2721,17 @@
     <row r="71" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="51"/>
       <c r="B71" s="3"/>
-      <c r="C71" s="59"/>
+      <c r="C71" s="48"/>
       <c r="D71" s="13" t="s">
         <v>74</v>
       </c>
       <c r="E71" s="11"/>
-      <c r="F71" s="47" t="s">
+      <c r="F71" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="G71" s="45"/>
+      <c r="G71" s="46"/>
       <c r="H71" s="11"/>
-      <c r="I71" s="61"/>
+      <c r="I71" s="64"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
@@ -2759,17 +2739,17 @@
     <row r="72" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="51"/>
       <c r="B72" s="3"/>
-      <c r="C72" s="59"/>
+      <c r="C72" s="48"/>
       <c r="D72" s="13" t="s">
         <v>76</v>
       </c>
       <c r="E72" s="26"/>
-      <c r="F72" s="47" t="s">
+      <c r="F72" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G72" s="45"/>
+      <c r="G72" s="46"/>
       <c r="H72" s="26"/>
-      <c r="I72" s="61"/>
+      <c r="I72" s="64"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
@@ -2777,15 +2757,15 @@
     <row r="73" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="51"/>
       <c r="B73" s="3"/>
-      <c r="C73" s="65" t="s">
+      <c r="C73" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="D73" s="45"/>
+      <c r="D73" s="46"/>
       <c r="E73" s="24"/>
-      <c r="F73" s="70" t="s">
+      <c r="F73" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="G73" s="45"/>
+      <c r="G73" s="46"/>
       <c r="H73" s="24"/>
       <c r="I73" s="16" t="s">
         <v>42</v>
@@ -2796,34 +2776,34 @@
     </row>
     <row r="74" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="51"/>
-      <c r="B74" s="53" t="s">
+      <c r="B74" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="C74" s="44"/>
-      <c r="D74" s="44"/>
-      <c r="E74" s="44"/>
-      <c r="F74" s="44"/>
-      <c r="G74" s="44"/>
-      <c r="H74" s="44"/>
-      <c r="I74" s="45"/>
+      <c r="C74" s="45"/>
+      <c r="D74" s="45"/>
+      <c r="E74" s="45"/>
+      <c r="F74" s="45"/>
+      <c r="G74" s="45"/>
+      <c r="H74" s="45"/>
+      <c r="I74" s="46"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
     </row>
     <row r="75" spans="1:12" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="63">
+      <c r="A75" s="50">
         <v>11</v>
       </c>
-      <c r="B75" s="97" t="s">
+      <c r="B75" s="96" t="s">
         <v>78</v>
       </c>
-      <c r="C75" s="44"/>
-      <c r="D75" s="44"/>
-      <c r="E75" s="44"/>
-      <c r="F75" s="44"/>
-      <c r="G75" s="44"/>
-      <c r="H75" s="44"/>
-      <c r="I75" s="45"/>
+      <c r="C75" s="45"/>
+      <c r="D75" s="45"/>
+      <c r="E75" s="45"/>
+      <c r="F75" s="45"/>
+      <c r="G75" s="45"/>
+      <c r="H75" s="45"/>
+      <c r="I75" s="46"/>
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
       <c r="L75" s="2"/>
@@ -2837,12 +2817,12 @@
       <c r="D76" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="E76" s="90"/>
-      <c r="F76" s="47" t="s">
+      <c r="E76" s="83"/>
+      <c r="F76" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="G76" s="45"/>
-      <c r="H76" s="50"/>
+      <c r="G76" s="46"/>
+      <c r="H76" s="78"/>
       <c r="I76" s="8" t="s">
         <v>81</v>
       </c>
@@ -2860,10 +2840,10 @@
         <v>83</v>
       </c>
       <c r="E77" s="51"/>
-      <c r="F77" s="47" t="s">
+      <c r="F77" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="G77" s="45"/>
+      <c r="G77" s="46"/>
       <c r="H77" s="51"/>
       <c r="I77" s="8" t="s">
         <v>84</v>
@@ -2882,10 +2862,10 @@
         <v>85</v>
       </c>
       <c r="E78" s="51"/>
-      <c r="F78" s="47" t="s">
+      <c r="F78" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="G78" s="45"/>
+      <c r="G78" s="46"/>
       <c r="H78" s="51"/>
       <c r="I78" s="8" t="s">
         <v>84</v>
@@ -2904,10 +2884,10 @@
         <v>85</v>
       </c>
       <c r="E79" s="14"/>
-      <c r="F79" s="47" t="s">
+      <c r="F79" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="G79" s="45"/>
+      <c r="G79" s="46"/>
       <c r="H79" s="51"/>
       <c r="I79" s="8" t="s">
         <v>84</v>
@@ -2919,16 +2899,16 @@
     <row r="80" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="51"/>
       <c r="B80" s="3"/>
-      <c r="C80" s="65" t="s">
+      <c r="C80" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="D80" s="45"/>
+      <c r="D80" s="46"/>
       <c r="E80" s="15"/>
-      <c r="F80" s="70" t="s">
+      <c r="F80" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="G80" s="45"/>
-      <c r="H80" s="52"/>
+      <c r="G80" s="46"/>
+      <c r="H80" s="65"/>
       <c r="I80" s="16" t="s">
         <v>42</v>
       </c>
@@ -2938,22 +2918,22 @@
     </row>
     <row r="81" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="51"/>
-      <c r="B81" s="53" t="s">
+      <c r="B81" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C81" s="44"/>
-      <c r="D81" s="44"/>
-      <c r="E81" s="44"/>
-      <c r="F81" s="44"/>
-      <c r="G81" s="44"/>
-      <c r="H81" s="44"/>
-      <c r="I81" s="45"/>
+      <c r="C81" s="45"/>
+      <c r="D81" s="45"/>
+      <c r="E81" s="45"/>
+      <c r="F81" s="45"/>
+      <c r="G81" s="45"/>
+      <c r="H81" s="45"/>
+      <c r="I81" s="46"/>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
     </row>
     <row r="82" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="63">
+      <c r="A82" s="50">
         <v>12</v>
       </c>
       <c r="B82" s="3"/>
@@ -2964,12 +2944,12 @@
         <v>87</v>
       </c>
       <c r="E82" s="7"/>
-      <c r="F82" s="47" t="s">
+      <c r="F82" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="G82" s="45"/>
-      <c r="H82" s="50"/>
-      <c r="I82" s="71" t="s">
+      <c r="G82" s="46"/>
+      <c r="H82" s="78"/>
+      <c r="I82" s="66" t="s">
         <v>84</v>
       </c>
       <c r="J82" s="2"/>
@@ -2986,10 +2966,10 @@
         <v>87</v>
       </c>
       <c r="E83" s="11"/>
-      <c r="F83" s="47" t="s">
+      <c r="F83" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="G83" s="45"/>
+      <c r="G83" s="46"/>
       <c r="H83" s="51"/>
       <c r="I83" s="51"/>
       <c r="J83" s="2"/>
@@ -3006,10 +2986,10 @@
         <v>89</v>
       </c>
       <c r="E84" s="11"/>
-      <c r="F84" s="47" t="s">
+      <c r="F84" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="G84" s="45"/>
+      <c r="G84" s="46"/>
       <c r="H84" s="51"/>
       <c r="I84" s="51"/>
       <c r="J84" s="2"/>
@@ -3026,12 +3006,12 @@
         <v>89</v>
       </c>
       <c r="E85" s="11"/>
-      <c r="F85" s="47" t="s">
+      <c r="F85" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="G85" s="45"/>
-      <c r="H85" s="52"/>
-      <c r="I85" s="52"/>
+      <c r="G85" s="46"/>
+      <c r="H85" s="65"/>
+      <c r="I85" s="65"/>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
@@ -3039,15 +3019,15 @@
     <row r="86" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="51"/>
       <c r="B86" s="3"/>
-      <c r="C86" s="65" t="s">
+      <c r="C86" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="D86" s="45"/>
+      <c r="D86" s="46"/>
       <c r="E86" s="15"/>
-      <c r="F86" s="70" t="s">
+      <c r="F86" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="G86" s="45"/>
+      <c r="G86" s="46"/>
       <c r="H86" s="23"/>
       <c r="I86" s="16" t="s">
         <v>42</v>
@@ -3058,22 +3038,22 @@
     </row>
     <row r="87" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="51"/>
-      <c r="B87" s="53" t="s">
+      <c r="B87" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C87" s="44"/>
-      <c r="D87" s="44"/>
-      <c r="E87" s="44"/>
-      <c r="F87" s="44"/>
-      <c r="G87" s="44"/>
-      <c r="H87" s="44"/>
-      <c r="I87" s="45"/>
+      <c r="C87" s="45"/>
+      <c r="D87" s="45"/>
+      <c r="E87" s="45"/>
+      <c r="F87" s="45"/>
+      <c r="G87" s="45"/>
+      <c r="H87" s="45"/>
+      <c r="I87" s="46"/>
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
       <c r="L87" s="2"/>
     </row>
     <row r="88" spans="1:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="63">
+      <c r="A88" s="50">
         <v>13</v>
       </c>
       <c r="B88" s="17"/>
@@ -3084,12 +3064,12 @@
         <v>91</v>
       </c>
       <c r="E88" s="7"/>
-      <c r="F88" s="73" t="s">
+      <c r="F88" s="79" t="s">
         <v>91</v>
       </c>
-      <c r="G88" s="45"/>
+      <c r="G88" s="46"/>
       <c r="H88" s="7"/>
-      <c r="I88" s="98" t="s">
+      <c r="I88" s="73" t="s">
         <v>84</v>
       </c>
       <c r="J88" s="2" t="s">
@@ -3108,10 +3088,10 @@
         <v>94</v>
       </c>
       <c r="E89" s="11"/>
-      <c r="F89" s="47" t="s">
+      <c r="F89" s="49" t="s">
         <v>94</v>
       </c>
-      <c r="G89" s="45"/>
+      <c r="G89" s="46"/>
       <c r="H89" s="11"/>
       <c r="I89" s="51"/>
       <c r="J89" s="2"/>
@@ -3128,10 +3108,10 @@
         <v>94</v>
       </c>
       <c r="E90" s="11"/>
-      <c r="F90" s="47" t="s">
+      <c r="F90" s="49" t="s">
         <v>94</v>
       </c>
-      <c r="G90" s="45"/>
+      <c r="G90" s="46"/>
       <c r="H90" s="11"/>
       <c r="I90" s="51"/>
       <c r="J90" s="1"/>
@@ -3148,10 +3128,10 @@
         <v>94</v>
       </c>
       <c r="E91" s="11"/>
-      <c r="F91" s="47" t="s">
+      <c r="F91" s="49" t="s">
         <v>94</v>
       </c>
-      <c r="G91" s="45"/>
+      <c r="G91" s="46"/>
       <c r="H91" s="18"/>
       <c r="I91" s="51"/>
       <c r="J91" s="1"/>
@@ -3161,15 +3141,15 @@
     <row r="92" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="51"/>
       <c r="B92" s="17"/>
-      <c r="C92" s="47" t="s">
+      <c r="C92" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="D92" s="45"/>
+      <c r="D92" s="46"/>
       <c r="E92" s="11"/>
-      <c r="F92" s="92" t="s">
+      <c r="F92" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="G92" s="45"/>
+      <c r="G92" s="46"/>
       <c r="H92" s="19"/>
       <c r="I92" s="20" t="s">
         <v>42</v>
@@ -3180,22 +3160,22 @@
     </row>
     <row r="93" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="51"/>
-      <c r="B93" s="53" t="s">
+      <c r="B93" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C93" s="44"/>
-      <c r="D93" s="44"/>
-      <c r="E93" s="44"/>
-      <c r="F93" s="44"/>
-      <c r="G93" s="44"/>
-      <c r="H93" s="44"/>
-      <c r="I93" s="45"/>
+      <c r="C93" s="45"/>
+      <c r="D93" s="45"/>
+      <c r="E93" s="45"/>
+      <c r="F93" s="45"/>
+      <c r="G93" s="45"/>
+      <c r="H93" s="45"/>
+      <c r="I93" s="46"/>
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
     </row>
     <row r="94" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="63">
+      <c r="A94" s="50">
         <v>14</v>
       </c>
       <c r="B94" s="17"/>
@@ -3205,13 +3185,13 @@
       <c r="D94" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="E94" s="50"/>
-      <c r="F94" s="66" t="s">
+      <c r="E94" s="78"/>
+      <c r="F94" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="G94" s="45"/>
-      <c r="H94" s="50"/>
-      <c r="I94" s="71" t="s">
+      <c r="G94" s="46"/>
+      <c r="H94" s="78"/>
+      <c r="I94" s="66" t="s">
         <v>84</v>
       </c>
       <c r="J94" s="2"/>
@@ -3228,10 +3208,10 @@
         <v>97</v>
       </c>
       <c r="E95" s="51"/>
-      <c r="F95" s="47" t="s">
+      <c r="F95" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="G95" s="45"/>
+      <c r="G95" s="46"/>
       <c r="H95" s="51"/>
       <c r="I95" s="51"/>
       <c r="J95" s="2"/>
@@ -3248,12 +3228,12 @@
         <v>97</v>
       </c>
       <c r="E96" s="51"/>
-      <c r="F96" s="47" t="s">
+      <c r="F96" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="G96" s="45"/>
+      <c r="G96" s="46"/>
       <c r="H96" s="51"/>
-      <c r="I96" s="52"/>
+      <c r="I96" s="65"/>
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
       <c r="L96" s="2"/>
@@ -3268,12 +3248,12 @@
         <v>99</v>
       </c>
       <c r="E97" s="51"/>
-      <c r="F97" s="47" t="s">
+      <c r="F97" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="G97" s="45"/>
+      <c r="G97" s="46"/>
       <c r="H97" s="51"/>
-      <c r="I97" s="93" t="s">
+      <c r="I97" s="81" t="s">
         <v>42</v>
       </c>
       <c r="J97" s="2"/>
@@ -3283,15 +3263,15 @@
     <row r="98" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="51"/>
       <c r="B98" s="17"/>
-      <c r="C98" s="47" t="s">
+      <c r="C98" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="D98" s="45"/>
+      <c r="D98" s="46"/>
       <c r="E98" s="51"/>
-      <c r="F98" s="114" t="s">
+      <c r="F98" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="G98" s="58"/>
+      <c r="G98" s="69"/>
       <c r="H98" s="51"/>
       <c r="I98" s="51"/>
       <c r="J98" s="21"/>
@@ -3301,35 +3281,35 @@
     <row r="99" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="51"/>
       <c r="B99" s="17"/>
-      <c r="C99" s="47"/>
-      <c r="D99" s="45"/>
-      <c r="E99" s="52"/>
-      <c r="F99" s="67"/>
-      <c r="G99" s="69"/>
-      <c r="H99" s="52"/>
-      <c r="I99" s="52"/>
+      <c r="C99" s="49"/>
+      <c r="D99" s="46"/>
+      <c r="E99" s="65"/>
+      <c r="F99" s="54"/>
+      <c r="G99" s="71"/>
+      <c r="H99" s="65"/>
+      <c r="I99" s="65"/>
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
       <c r="L99" s="2"/>
     </row>
     <row r="100" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="51"/>
-      <c r="B100" s="53" t="s">
+      <c r="B100" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C100" s="44"/>
-      <c r="D100" s="44"/>
-      <c r="E100" s="44"/>
-      <c r="F100" s="44"/>
-      <c r="G100" s="44"/>
-      <c r="H100" s="44"/>
-      <c r="I100" s="45"/>
+      <c r="C100" s="45"/>
+      <c r="D100" s="45"/>
+      <c r="E100" s="45"/>
+      <c r="F100" s="45"/>
+      <c r="G100" s="45"/>
+      <c r="H100" s="45"/>
+      <c r="I100" s="46"/>
       <c r="J100" s="2"/>
       <c r="K100" s="2"/>
       <c r="L100" s="2"/>
     </row>
     <row r="101" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="63">
+      <c r="A101" s="50">
         <v>15</v>
       </c>
       <c r="B101" s="3"/>
@@ -3339,13 +3319,13 @@
       <c r="D101" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="E101" s="50"/>
-      <c r="F101" s="86" t="s">
+      <c r="E101" s="78"/>
+      <c r="F101" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="G101" s="45"/>
-      <c r="H101" s="50"/>
-      <c r="I101" s="71" t="s">
+      <c r="G101" s="46"/>
+      <c r="H101" s="78"/>
+      <c r="I101" s="66" t="s">
         <v>84</v>
       </c>
       <c r="J101" s="1"/>
@@ -3362,10 +3342,10 @@
         <v>99</v>
       </c>
       <c r="E102" s="51"/>
-      <c r="F102" s="86" t="s">
+      <c r="F102" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="G102" s="45"/>
+      <c r="G102" s="46"/>
       <c r="H102" s="51"/>
       <c r="I102" s="51"/>
       <c r="J102" s="2"/>
@@ -3382,12 +3362,12 @@
         <v>102</v>
       </c>
       <c r="E103" s="51"/>
-      <c r="F103" s="54" t="s">
+      <c r="F103" s="82" t="s">
         <v>102</v>
       </c>
-      <c r="G103" s="55"/>
+      <c r="G103" s="53"/>
       <c r="H103" s="51"/>
-      <c r="I103" s="52"/>
+      <c r="I103" s="65"/>
       <c r="J103" s="2"/>
       <c r="K103" s="2"/>
       <c r="L103" s="2"/>
@@ -3402,12 +3382,12 @@
         <v>102</v>
       </c>
       <c r="E104" s="51"/>
-      <c r="F104" s="54" t="s">
+      <c r="F104" s="82" t="s">
         <v>102</v>
       </c>
-      <c r="G104" s="55"/>
+      <c r="G104" s="53"/>
       <c r="H104" s="51"/>
-      <c r="I104" s="93" t="s">
+      <c r="I104" s="81" t="s">
         <v>42</v>
       </c>
       <c r="J104" s="2"/>
@@ -3417,15 +3397,15 @@
     <row r="105" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="51"/>
       <c r="B105" s="35"/>
-      <c r="C105" s="78" t="s">
+      <c r="C105" s="102" t="s">
         <v>14</v>
       </c>
-      <c r="D105" s="79"/>
+      <c r="D105" s="103"/>
       <c r="E105" s="51"/>
-      <c r="F105" s="78" t="s">
+      <c r="F105" s="102" t="s">
         <v>60</v>
       </c>
-      <c r="G105" s="79"/>
+      <c r="G105" s="103"/>
       <c r="H105" s="51"/>
       <c r="I105" s="51"/>
       <c r="J105" s="2"/>
@@ -3435,35 +3415,35 @@
     <row r="106" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="51"/>
       <c r="B106" s="37"/>
-      <c r="C106" s="80"/>
-      <c r="D106" s="81"/>
-      <c r="E106" s="52"/>
-      <c r="F106" s="80"/>
-      <c r="G106" s="81"/>
-      <c r="H106" s="52"/>
-      <c r="I106" s="52"/>
+      <c r="C106" s="104"/>
+      <c r="D106" s="105"/>
+      <c r="E106" s="65"/>
+      <c r="F106" s="104"/>
+      <c r="G106" s="105"/>
+      <c r="H106" s="65"/>
+      <c r="I106" s="65"/>
       <c r="J106" s="2"/>
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
     </row>
     <row r="107" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="51"/>
-      <c r="B107" s="53" t="s">
+      <c r="B107" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C107" s="44"/>
-      <c r="D107" s="44"/>
-      <c r="E107" s="44"/>
-      <c r="F107" s="44"/>
-      <c r="G107" s="44"/>
-      <c r="H107" s="44"/>
-      <c r="I107" s="45"/>
+      <c r="C107" s="45"/>
+      <c r="D107" s="45"/>
+      <c r="E107" s="45"/>
+      <c r="F107" s="45"/>
+      <c r="G107" s="45"/>
+      <c r="H107" s="45"/>
+      <c r="I107" s="46"/>
       <c r="J107" s="2"/>
       <c r="K107" s="2"/>
       <c r="L107" s="2"/>
     </row>
     <row r="108" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="63">
+      <c r="A108" s="50">
         <v>16</v>
       </c>
       <c r="B108" s="3"/>
@@ -3474,12 +3454,12 @@
         <v>104</v>
       </c>
       <c r="E108" s="7"/>
-      <c r="F108" s="47" t="s">
+      <c r="F108" s="49" t="s">
         <v>104</v>
       </c>
-      <c r="G108" s="45"/>
-      <c r="H108" s="90"/>
-      <c r="I108" s="71" t="s">
+      <c r="G108" s="46"/>
+      <c r="H108" s="83"/>
+      <c r="I108" s="66" t="s">
         <v>84</v>
       </c>
       <c r="J108" s="2"/>
@@ -3496,10 +3476,10 @@
         <v>106</v>
       </c>
       <c r="E109" s="11"/>
-      <c r="F109" s="47" t="s">
+      <c r="F109" s="49" t="s">
         <v>106</v>
       </c>
-      <c r="G109" s="45"/>
+      <c r="G109" s="46"/>
       <c r="H109" s="51"/>
       <c r="I109" s="51"/>
       <c r="J109" s="2"/>
@@ -3516,10 +3496,10 @@
         <v>108</v>
       </c>
       <c r="E110" s="11"/>
-      <c r="F110" s="47" t="s">
+      <c r="F110" s="49" t="s">
         <v>108</v>
       </c>
-      <c r="G110" s="45"/>
+      <c r="G110" s="46"/>
       <c r="H110" s="51"/>
       <c r="I110" s="51"/>
       <c r="J110" s="2"/>
@@ -3536,12 +3516,12 @@
         <v>108</v>
       </c>
       <c r="E111" s="11"/>
-      <c r="F111" s="47" t="s">
+      <c r="F111" s="49" t="s">
         <v>108</v>
       </c>
-      <c r="G111" s="45"/>
+      <c r="G111" s="46"/>
       <c r="H111" s="51"/>
-      <c r="I111" s="52"/>
+      <c r="I111" s="65"/>
       <c r="J111" s="2"/>
       <c r="K111" s="2"/>
       <c r="L111" s="2"/>
@@ -3549,15 +3529,15 @@
     <row r="112" spans="1:12" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="51"/>
       <c r="B112" s="3"/>
-      <c r="C112" s="65" t="s">
+      <c r="C112" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="D112" s="45"/>
+      <c r="D112" s="46"/>
       <c r="E112" s="15"/>
-      <c r="F112" s="92" t="s">
+      <c r="F112" s="76" t="s">
         <v>109</v>
       </c>
-      <c r="G112" s="45"/>
+      <c r="G112" s="46"/>
       <c r="H112" s="26"/>
       <c r="I112" s="27" t="s">
         <v>42</v>
@@ -3582,22 +3562,22 @@
     </row>
     <row r="114" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="51"/>
-      <c r="B114" s="53" t="s">
+      <c r="B114" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C114" s="44"/>
-      <c r="D114" s="44"/>
-      <c r="E114" s="44"/>
-      <c r="F114" s="44"/>
-      <c r="G114" s="44"/>
-      <c r="H114" s="44"/>
-      <c r="I114" s="45"/>
+      <c r="C114" s="45"/>
+      <c r="D114" s="45"/>
+      <c r="E114" s="45"/>
+      <c r="F114" s="45"/>
+      <c r="G114" s="45"/>
+      <c r="H114" s="45"/>
+      <c r="I114" s="46"/>
       <c r="J114" s="2"/>
       <c r="K114" s="2"/>
       <c r="L114" s="2"/>
     </row>
     <row r="115" spans="1:12" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="63">
+      <c r="A115" s="50">
         <v>17</v>
       </c>
       <c r="B115" s="3"/>
@@ -3607,13 +3587,13 @@
       <c r="D115" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="E115" s="50"/>
-      <c r="F115" s="47" t="s">
+      <c r="E115" s="78"/>
+      <c r="F115" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="G115" s="45"/>
-      <c r="H115" s="50"/>
-      <c r="I115" s="71" t="s">
+      <c r="G115" s="46"/>
+      <c r="H115" s="78"/>
+      <c r="I115" s="66" t="s">
         <v>84</v>
       </c>
       <c r="J115" s="2" t="s">
@@ -3632,10 +3612,10 @@
         <v>111</v>
       </c>
       <c r="E116" s="51"/>
-      <c r="F116" s="47" t="s">
+      <c r="F116" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="G116" s="45"/>
+      <c r="G116" s="46"/>
       <c r="H116" s="51"/>
       <c r="I116" s="51"/>
       <c r="J116" s="2"/>
@@ -3652,10 +3632,10 @@
         <v>111</v>
       </c>
       <c r="E117" s="51"/>
-      <c r="F117" s="47" t="s">
+      <c r="F117" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="G117" s="45"/>
+      <c r="G117" s="46"/>
       <c r="H117" s="51"/>
       <c r="I117" s="51"/>
       <c r="J117" s="1"/>
@@ -3672,12 +3652,12 @@
         <v>114</v>
       </c>
       <c r="E118" s="51"/>
-      <c r="F118" s="47" t="s">
+      <c r="F118" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="G118" s="45"/>
+      <c r="G118" s="46"/>
       <c r="H118" s="51"/>
-      <c r="I118" s="52"/>
+      <c r="I118" s="65"/>
       <c r="J118" s="9"/>
       <c r="K118" s="2"/>
       <c r="L118" s="2"/>
@@ -3685,16 +3665,16 @@
     <row r="119" spans="1:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="51"/>
       <c r="B119" s="3"/>
-      <c r="C119" s="47" t="s">
+      <c r="C119" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="D119" s="45"/>
-      <c r="E119" s="52"/>
-      <c r="F119" s="103" t="s">
+      <c r="D119" s="46"/>
+      <c r="E119" s="65"/>
+      <c r="F119" s="86" t="s">
         <v>115</v>
       </c>
-      <c r="G119" s="45"/>
-      <c r="H119" s="52"/>
+      <c r="G119" s="46"/>
+      <c r="H119" s="65"/>
       <c r="I119" s="20" t="s">
         <v>42</v>
       </c>
@@ -3704,38 +3684,30 @@
     </row>
     <row r="120" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="51"/>
-      <c r="B120" s="53" t="s">
+      <c r="B120" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C120" s="44"/>
-      <c r="D120" s="44"/>
-      <c r="E120" s="44"/>
-      <c r="F120" s="44"/>
-      <c r="G120" s="44"/>
-      <c r="H120" s="44"/>
-      <c r="I120" s="45"/>
+      <c r="C120" s="45"/>
+      <c r="D120" s="45"/>
+      <c r="E120" s="45"/>
+      <c r="F120" s="45"/>
+      <c r="G120" s="45"/>
+      <c r="H120" s="45"/>
+      <c r="I120" s="46"/>
       <c r="J120" s="2"/>
       <c r="K120" s="2"/>
       <c r="L120" s="2"/>
     </row>
     <row r="121" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="63">
-        <v>18</v>
-      </c>
+      <c r="A121" s="115"/>
       <c r="B121" s="3"/>
-      <c r="C121" s="56" t="s">
-        <v>116</v>
-      </c>
-      <c r="D121" s="45"/>
-      <c r="E121" s="50"/>
-      <c r="F121" s="56" t="s">
-        <v>116</v>
-      </c>
-      <c r="G121" s="45"/>
-      <c r="H121" s="50"/>
-      <c r="I121" s="71" t="s">
-        <v>84</v>
-      </c>
+      <c r="C121" s="118"/>
+      <c r="D121" s="42"/>
+      <c r="E121" s="116"/>
+      <c r="F121" s="118"/>
+      <c r="G121" s="42"/>
+      <c r="H121" s="116"/>
+      <c r="I121" s="117"/>
       <c r="J121" s="2"/>
       <c r="K121" s="2"/>
       <c r="L121" s="2"/>
@@ -3744,16 +3716,16 @@
       <c r="A122" s="51"/>
       <c r="B122" s="3"/>
       <c r="C122" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D122" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="D122" s="13" t="s">
-        <v>118</v>
-      </c>
       <c r="E122" s="51"/>
-      <c r="F122" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="G122" s="45"/>
+      <c r="F122" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="G122" s="46"/>
       <c r="H122" s="51"/>
       <c r="I122" s="51"/>
       <c r="J122" s="2"/>
@@ -3764,18 +3736,18 @@
       <c r="A123" s="51"/>
       <c r="B123" s="3"/>
       <c r="C123" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D123" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="D123" s="13" t="s">
-        <v>118</v>
-      </c>
       <c r="E123" s="51"/>
-      <c r="F123" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="G123" s="45"/>
+      <c r="F123" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="G123" s="46"/>
       <c r="H123" s="51"/>
-      <c r="I123" s="52"/>
+      <c r="I123" s="65"/>
       <c r="J123" s="2"/>
       <c r="K123" s="2"/>
       <c r="L123" s="2"/>
@@ -3784,18 +3756,18 @@
       <c r="A124" s="51"/>
       <c r="B124" s="3"/>
       <c r="C124" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D124" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="D124" s="13" t="s">
-        <v>118</v>
-      </c>
       <c r="E124" s="51"/>
-      <c r="F124" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="G124" s="45"/>
+      <c r="F124" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="G124" s="46"/>
       <c r="H124" s="51"/>
-      <c r="I124" s="93" t="s">
+      <c r="I124" s="81" t="s">
         <v>42</v>
       </c>
       <c r="J124" s="2"/>
@@ -3805,15 +3777,15 @@
     <row r="125" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="51"/>
       <c r="B125" s="3"/>
-      <c r="C125" s="47" t="s">
+      <c r="C125" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="D125" s="45"/>
+      <c r="D125" s="46"/>
       <c r="E125" s="51"/>
-      <c r="F125" s="105" t="s">
-        <v>119</v>
-      </c>
-      <c r="G125" s="58"/>
+      <c r="F125" s="75" t="s">
+        <v>118</v>
+      </c>
+      <c r="G125" s="69"/>
       <c r="H125" s="51"/>
       <c r="I125" s="51"/>
       <c r="J125" s="2"/>
@@ -3823,47 +3795,47 @@
     <row r="126" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="51"/>
       <c r="B126" s="3"/>
-      <c r="C126" s="47"/>
-      <c r="D126" s="45"/>
-      <c r="E126" s="52"/>
-      <c r="F126" s="67"/>
-      <c r="G126" s="69"/>
-      <c r="H126" s="52"/>
-      <c r="I126" s="52"/>
+      <c r="C126" s="49"/>
+      <c r="D126" s="46"/>
+      <c r="E126" s="65"/>
+      <c r="F126" s="54"/>
+      <c r="G126" s="71"/>
+      <c r="H126" s="65"/>
+      <c r="I126" s="65"/>
       <c r="J126" s="2"/>
       <c r="K126" s="2"/>
       <c r="L126" s="2"/>
     </row>
     <row r="127" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="51"/>
-      <c r="B127" s="53" t="s">
+      <c r="B127" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C127" s="44"/>
-      <c r="D127" s="44"/>
-      <c r="E127" s="44"/>
-      <c r="F127" s="44"/>
-      <c r="G127" s="44"/>
-      <c r="H127" s="44"/>
-      <c r="I127" s="45"/>
+      <c r="C127" s="45"/>
+      <c r="D127" s="45"/>
+      <c r="E127" s="45"/>
+      <c r="F127" s="45"/>
+      <c r="G127" s="45"/>
+      <c r="H127" s="45"/>
+      <c r="I127" s="46"/>
       <c r="J127" s="2"/>
       <c r="K127" s="2"/>
       <c r="L127" s="2"/>
     </row>
     <row r="128" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="63">
+      <c r="A128" s="50">
         <v>19</v>
       </c>
       <c r="B128" s="3"/>
-      <c r="C128" s="113" t="s">
-        <v>120</v>
-      </c>
-      <c r="D128" s="58"/>
-      <c r="E128" s="58"/>
-      <c r="F128" s="58"/>
-      <c r="G128" s="58"/>
-      <c r="H128" s="58"/>
-      <c r="I128" s="55"/>
+      <c r="C128" s="68" t="s">
+        <v>119</v>
+      </c>
+      <c r="D128" s="69"/>
+      <c r="E128" s="69"/>
+      <c r="F128" s="69"/>
+      <c r="G128" s="69"/>
+      <c r="H128" s="69"/>
+      <c r="I128" s="53"/>
       <c r="J128" s="2"/>
       <c r="K128" s="2"/>
       <c r="L128" s="2"/>
@@ -3871,13 +3843,13 @@
     <row r="129" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="51"/>
       <c r="B129" s="3"/>
-      <c r="C129" s="59"/>
-      <c r="D129" s="60"/>
-      <c r="E129" s="60"/>
-      <c r="F129" s="60"/>
-      <c r="G129" s="60"/>
-      <c r="H129" s="60"/>
-      <c r="I129" s="61"/>
+      <c r="C129" s="48"/>
+      <c r="D129" s="70"/>
+      <c r="E129" s="70"/>
+      <c r="F129" s="70"/>
+      <c r="G129" s="70"/>
+      <c r="H129" s="70"/>
+      <c r="I129" s="64"/>
       <c r="J129" s="2"/>
       <c r="K129" s="2"/>
       <c r="L129" s="2"/>
@@ -3885,13 +3857,13 @@
     <row r="130" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="51"/>
       <c r="B130" s="3"/>
-      <c r="C130" s="59"/>
-      <c r="D130" s="60"/>
-      <c r="E130" s="60"/>
-      <c r="F130" s="60"/>
-      <c r="G130" s="60"/>
-      <c r="H130" s="60"/>
-      <c r="I130" s="61"/>
+      <c r="C130" s="48"/>
+      <c r="D130" s="70"/>
+      <c r="E130" s="70"/>
+      <c r="F130" s="70"/>
+      <c r="G130" s="70"/>
+      <c r="H130" s="70"/>
+      <c r="I130" s="64"/>
       <c r="J130" s="2"/>
       <c r="K130" s="2"/>
       <c r="L130" s="2"/>
@@ -3899,13 +3871,13 @@
     <row r="131" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="51"/>
       <c r="B131" s="3"/>
-      <c r="C131" s="59"/>
-      <c r="D131" s="60"/>
-      <c r="E131" s="60"/>
-      <c r="F131" s="60"/>
-      <c r="G131" s="60"/>
-      <c r="H131" s="60"/>
-      <c r="I131" s="61"/>
+      <c r="C131" s="48"/>
+      <c r="D131" s="70"/>
+      <c r="E131" s="70"/>
+      <c r="F131" s="70"/>
+      <c r="G131" s="70"/>
+      <c r="H131" s="70"/>
+      <c r="I131" s="64"/>
       <c r="J131" s="2"/>
       <c r="K131" s="2"/>
       <c r="L131" s="2"/>
@@ -3913,13 +3885,13 @@
     <row r="132" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="51"/>
       <c r="B132" s="3"/>
-      <c r="C132" s="59"/>
-      <c r="D132" s="60"/>
-      <c r="E132" s="60"/>
-      <c r="F132" s="60"/>
-      <c r="G132" s="60"/>
-      <c r="H132" s="60"/>
-      <c r="I132" s="61"/>
+      <c r="C132" s="48"/>
+      <c r="D132" s="70"/>
+      <c r="E132" s="70"/>
+      <c r="F132" s="70"/>
+      <c r="G132" s="70"/>
+      <c r="H132" s="70"/>
+      <c r="I132" s="64"/>
       <c r="J132" s="21"/>
       <c r="K132" s="21"/>
       <c r="L132" s="21"/>
@@ -3927,47 +3899,47 @@
     <row r="133" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="51"/>
       <c r="B133" s="3"/>
-      <c r="C133" s="67"/>
-      <c r="D133" s="69"/>
-      <c r="E133" s="69"/>
-      <c r="F133" s="69"/>
-      <c r="G133" s="69"/>
-      <c r="H133" s="69"/>
-      <c r="I133" s="49"/>
+      <c r="C133" s="54"/>
+      <c r="D133" s="71"/>
+      <c r="E133" s="71"/>
+      <c r="F133" s="71"/>
+      <c r="G133" s="71"/>
+      <c r="H133" s="71"/>
+      <c r="I133" s="55"/>
       <c r="J133" s="2"/>
       <c r="K133" s="2"/>
       <c r="L133" s="2"/>
     </row>
     <row r="134" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="51"/>
-      <c r="B134" s="53" t="s">
+      <c r="B134" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C134" s="44"/>
-      <c r="D134" s="44"/>
-      <c r="E134" s="44"/>
-      <c r="F134" s="44"/>
-      <c r="G134" s="44"/>
-      <c r="H134" s="44"/>
-      <c r="I134" s="45"/>
+      <c r="C134" s="45"/>
+      <c r="D134" s="45"/>
+      <c r="E134" s="45"/>
+      <c r="F134" s="45"/>
+      <c r="G134" s="45"/>
+      <c r="H134" s="45"/>
+      <c r="I134" s="46"/>
       <c r="J134" s="2"/>
       <c r="K134" s="2"/>
       <c r="L134" s="2"/>
     </row>
     <row r="135" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="63">
+      <c r="A135" s="50">
         <v>20</v>
       </c>
       <c r="B135" s="3"/>
-      <c r="C135" s="57" t="s">
-        <v>121</v>
-      </c>
-      <c r="D135" s="58"/>
-      <c r="E135" s="58"/>
-      <c r="F135" s="58"/>
-      <c r="G135" s="58"/>
-      <c r="H135" s="58"/>
-      <c r="I135" s="55"/>
+      <c r="C135" s="114" t="s">
+        <v>120</v>
+      </c>
+      <c r="D135" s="69"/>
+      <c r="E135" s="69"/>
+      <c r="F135" s="69"/>
+      <c r="G135" s="69"/>
+      <c r="H135" s="69"/>
+      <c r="I135" s="53"/>
       <c r="J135" s="2"/>
       <c r="K135" s="2"/>
       <c r="L135" s="2"/>
@@ -3975,13 +3947,13 @@
     <row r="136" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="51"/>
       <c r="B136" s="3"/>
-      <c r="C136" s="59"/>
-      <c r="D136" s="60"/>
-      <c r="E136" s="60"/>
-      <c r="F136" s="60"/>
-      <c r="G136" s="60"/>
-      <c r="H136" s="60"/>
-      <c r="I136" s="61"/>
+      <c r="C136" s="48"/>
+      <c r="D136" s="70"/>
+      <c r="E136" s="70"/>
+      <c r="F136" s="70"/>
+      <c r="G136" s="70"/>
+      <c r="H136" s="70"/>
+      <c r="I136" s="64"/>
       <c r="J136" s="2"/>
       <c r="K136" s="2"/>
       <c r="L136" s="2"/>
@@ -3989,79 +3961,75 @@
     <row r="137" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="51"/>
       <c r="B137" s="3"/>
-      <c r="C137" s="59"/>
-      <c r="D137" s="60"/>
-      <c r="E137" s="60"/>
-      <c r="F137" s="60"/>
-      <c r="G137" s="60"/>
-      <c r="H137" s="60"/>
-      <c r="I137" s="61"/>
+      <c r="C137" s="48"/>
+      <c r="D137" s="70"/>
+      <c r="E137" s="70"/>
+      <c r="F137" s="70"/>
+      <c r="G137" s="70"/>
+      <c r="H137" s="70"/>
+      <c r="I137" s="64"/>
       <c r="J137" s="1"/>
       <c r="K137" s="1"/>
       <c r="L137" s="1"/>
     </row>
-    <row r="138" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="51"/>
       <c r="B138" s="3"/>
-      <c r="C138" s="59"/>
-      <c r="D138" s="60"/>
-      <c r="E138" s="60"/>
-      <c r="F138" s="60"/>
-      <c r="G138" s="60"/>
-      <c r="H138" s="60"/>
-      <c r="I138" s="61"/>
-      <c r="J138" s="2"/>
-      <c r="K138" s="2"/>
-      <c r="L138" s="2"/>
+      <c r="C138" s="48"/>
+      <c r="D138" s="70"/>
+      <c r="E138" s="70"/>
+      <c r="F138" s="70"/>
+      <c r="G138" s="70"/>
+      <c r="H138" s="70"/>
+      <c r="I138" s="64"/>
+      <c r="J138" s="1"/>
+      <c r="K138" s="1"/>
+      <c r="L138" s="1"/>
     </row>
     <row r="139" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="51"/>
       <c r="B139" s="3"/>
-      <c r="C139" s="87" t="s">
-        <v>122</v>
-      </c>
-      <c r="D139" s="69"/>
-      <c r="E139" s="38"/>
-      <c r="F139" s="99" t="s">
-        <v>122</v>
-      </c>
-      <c r="G139" s="69"/>
-      <c r="H139" s="69"/>
-      <c r="I139" s="49"/>
+      <c r="C139" s="48"/>
+      <c r="D139" s="70"/>
+      <c r="E139" s="70"/>
+      <c r="F139" s="70"/>
+      <c r="G139" s="70"/>
+      <c r="H139" s="70"/>
+      <c r="I139" s="64"/>
       <c r="J139" s="2"/>
       <c r="K139" s="2"/>
       <c r="L139" s="2"/>
     </row>
     <row r="140" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="51"/>
-      <c r="B140" s="53" t="s">
+      <c r="B140" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C140" s="44"/>
-      <c r="D140" s="44"/>
-      <c r="E140" s="44"/>
-      <c r="F140" s="44"/>
-      <c r="G140" s="44"/>
-      <c r="H140" s="44"/>
-      <c r="I140" s="45"/>
+      <c r="C140" s="45"/>
+      <c r="D140" s="45"/>
+      <c r="E140" s="45"/>
+      <c r="F140" s="45"/>
+      <c r="G140" s="45"/>
+      <c r="H140" s="45"/>
+      <c r="I140" s="46"/>
       <c r="J140" s="2"/>
       <c r="K140" s="2"/>
       <c r="L140" s="2"/>
     </row>
     <row r="141" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="63">
+      <c r="A141" s="50">
         <v>21</v>
       </c>
       <c r="B141" s="3"/>
-      <c r="C141" s="104" t="s">
-        <v>121</v>
-      </c>
-      <c r="D141" s="58"/>
-      <c r="E141" s="58"/>
-      <c r="F141" s="58"/>
-      <c r="G141" s="58"/>
-      <c r="H141" s="58"/>
-      <c r="I141" s="55"/>
+      <c r="C141" s="74" t="s">
+        <v>120</v>
+      </c>
+      <c r="D141" s="69"/>
+      <c r="E141" s="69"/>
+      <c r="F141" s="69"/>
+      <c r="G141" s="69"/>
+      <c r="H141" s="69"/>
+      <c r="I141" s="53"/>
       <c r="J141" s="2"/>
       <c r="K141" s="2"/>
       <c r="L141" s="2"/>
@@ -4069,13 +4037,13 @@
     <row r="142" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="51"/>
       <c r="B142" s="3"/>
-      <c r="C142" s="59"/>
-      <c r="D142" s="60"/>
-      <c r="E142" s="60"/>
-      <c r="F142" s="60"/>
-      <c r="G142" s="60"/>
-      <c r="H142" s="60"/>
-      <c r="I142" s="61"/>
+      <c r="C142" s="48"/>
+      <c r="D142" s="70"/>
+      <c r="E142" s="70"/>
+      <c r="F142" s="70"/>
+      <c r="G142" s="70"/>
+      <c r="H142" s="70"/>
+      <c r="I142" s="64"/>
       <c r="J142" s="2"/>
       <c r="K142" s="2"/>
       <c r="L142" s="2"/>
@@ -4083,13 +4051,13 @@
     <row r="143" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="51"/>
       <c r="B143" s="3"/>
-      <c r="C143" s="59"/>
-      <c r="D143" s="60"/>
-      <c r="E143" s="60"/>
-      <c r="F143" s="60"/>
-      <c r="G143" s="60"/>
-      <c r="H143" s="60"/>
-      <c r="I143" s="61"/>
+      <c r="C143" s="48"/>
+      <c r="D143" s="70"/>
+      <c r="E143" s="70"/>
+      <c r="F143" s="70"/>
+      <c r="G143" s="70"/>
+      <c r="H143" s="70"/>
+      <c r="I143" s="64"/>
       <c r="J143" s="2"/>
       <c r="K143" s="2"/>
       <c r="L143" s="2"/>
@@ -4097,13 +4065,13 @@
     <row r="144" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="51"/>
       <c r="B144" s="3"/>
-      <c r="C144" s="67"/>
-      <c r="D144" s="69"/>
-      <c r="E144" s="69"/>
-      <c r="F144" s="69"/>
-      <c r="G144" s="69"/>
-      <c r="H144" s="69"/>
-      <c r="I144" s="49"/>
+      <c r="C144" s="54"/>
+      <c r="D144" s="71"/>
+      <c r="E144" s="71"/>
+      <c r="F144" s="71"/>
+      <c r="G144" s="71"/>
+      <c r="H144" s="71"/>
+      <c r="I144" s="55"/>
       <c r="J144" s="2"/>
       <c r="K144" s="2"/>
       <c r="L144" s="2"/>
@@ -4111,49 +4079,49 @@
     <row r="145" spans="1:12" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="51"/>
       <c r="B145" s="3"/>
-      <c r="C145" s="106" t="s">
-        <v>123</v>
-      </c>
-      <c r="D145" s="44"/>
-      <c r="E145" s="44"/>
-      <c r="F145" s="44"/>
-      <c r="G145" s="44"/>
-      <c r="H145" s="44"/>
-      <c r="I145" s="45"/>
+      <c r="C145" s="84" t="s">
+        <v>121</v>
+      </c>
+      <c r="D145" s="45"/>
+      <c r="E145" s="45"/>
+      <c r="F145" s="45"/>
+      <c r="G145" s="45"/>
+      <c r="H145" s="45"/>
+      <c r="I145" s="46"/>
       <c r="J145" s="2"/>
       <c r="K145" s="2"/>
       <c r="L145" s="2"/>
     </row>
     <row r="146" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="51"/>
-      <c r="B146" s="53" t="s">
+      <c r="B146" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C146" s="44"/>
-      <c r="D146" s="44"/>
-      <c r="E146" s="44"/>
-      <c r="F146" s="44"/>
-      <c r="G146" s="44"/>
-      <c r="H146" s="44"/>
-      <c r="I146" s="45"/>
+      <c r="C146" s="45"/>
+      <c r="D146" s="45"/>
+      <c r="E146" s="45"/>
+      <c r="F146" s="45"/>
+      <c r="G146" s="45"/>
+      <c r="H146" s="45"/>
+      <c r="I146" s="46"/>
       <c r="J146" s="2"/>
       <c r="K146" s="2"/>
       <c r="L146" s="2"/>
     </row>
     <row r="147" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="102">
+      <c r="A147" s="80">
         <v>22</v>
       </c>
       <c r="B147" s="3"/>
-      <c r="C147" s="43" t="s">
-        <v>124</v>
-      </c>
-      <c r="D147" s="44"/>
-      <c r="E147" s="44"/>
-      <c r="F147" s="44"/>
-      <c r="G147" s="44"/>
-      <c r="H147" s="44"/>
-      <c r="I147" s="45"/>
+      <c r="C147" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="D147" s="45"/>
+      <c r="E147" s="45"/>
+      <c r="F147" s="45"/>
+      <c r="G147" s="45"/>
+      <c r="H147" s="45"/>
+      <c r="I147" s="46"/>
       <c r="J147" s="2"/>
       <c r="K147" s="2"/>
       <c r="L147" s="2"/>
@@ -4161,15 +4129,15 @@
     <row r="148" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="51"/>
       <c r="B148" s="3"/>
-      <c r="C148" s="43" t="s">
-        <v>125</v>
-      </c>
-      <c r="D148" s="44"/>
-      <c r="E148" s="44"/>
-      <c r="F148" s="44"/>
-      <c r="G148" s="44"/>
-      <c r="H148" s="44"/>
-      <c r="I148" s="45"/>
+      <c r="C148" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="D148" s="45"/>
+      <c r="E148" s="45"/>
+      <c r="F148" s="45"/>
+      <c r="G148" s="45"/>
+      <c r="H148" s="45"/>
+      <c r="I148" s="46"/>
       <c r="J148" s="2"/>
       <c r="K148" s="2"/>
       <c r="L148" s="2"/>
@@ -4177,15 +4145,15 @@
     <row r="149" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="51"/>
       <c r="B149" s="3"/>
-      <c r="C149" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="D149" s="44"/>
-      <c r="E149" s="44"/>
-      <c r="F149" s="44"/>
-      <c r="G149" s="44"/>
-      <c r="H149" s="44"/>
-      <c r="I149" s="45"/>
+      <c r="C149" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="D149" s="45"/>
+      <c r="E149" s="45"/>
+      <c r="F149" s="45"/>
+      <c r="G149" s="45"/>
+      <c r="H149" s="45"/>
+      <c r="I149" s="46"/>
       <c r="J149" s="2"/>
       <c r="K149" s="2"/>
       <c r="L149" s="2"/>
@@ -4193,15 +4161,15 @@
     <row r="150" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="51"/>
       <c r="B150" s="3"/>
-      <c r="C150" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="D150" s="44"/>
-      <c r="E150" s="44"/>
-      <c r="F150" s="44"/>
-      <c r="G150" s="44"/>
-      <c r="H150" s="44"/>
-      <c r="I150" s="45"/>
+      <c r="C150" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="D150" s="45"/>
+      <c r="E150" s="45"/>
+      <c r="F150" s="45"/>
+      <c r="G150" s="45"/>
+      <c r="H150" s="45"/>
+      <c r="I150" s="46"/>
       <c r="J150" s="2"/>
       <c r="K150" s="2"/>
       <c r="L150" s="2"/>
@@ -4209,31 +4177,31 @@
     <row r="151" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="51"/>
       <c r="B151" s="3"/>
-      <c r="C151" s="43" t="s">
-        <v>125</v>
-      </c>
-      <c r="D151" s="44"/>
-      <c r="E151" s="44"/>
-      <c r="F151" s="44"/>
-      <c r="G151" s="44"/>
-      <c r="H151" s="44"/>
-      <c r="I151" s="45"/>
+      <c r="C151" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="D151" s="45"/>
+      <c r="E151" s="45"/>
+      <c r="F151" s="45"/>
+      <c r="G151" s="45"/>
+      <c r="H151" s="45"/>
+      <c r="I151" s="46"/>
       <c r="J151" s="1"/>
       <c r="K151" s="1"/>
       <c r="L151" s="1"/>
     </row>
     <row r="152" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="52"/>
+      <c r="A152" s="65"/>
       <c r="B152" s="3"/>
-      <c r="C152" s="47" t="s">
-        <v>127</v>
-      </c>
-      <c r="D152" s="44"/>
-      <c r="E152" s="44"/>
-      <c r="F152" s="44"/>
-      <c r="G152" s="44"/>
-      <c r="H152" s="44"/>
-      <c r="I152" s="45"/>
+      <c r="C152" s="49" t="s">
+        <v>125</v>
+      </c>
+      <c r="D152" s="45"/>
+      <c r="E152" s="45"/>
+      <c r="F152" s="45"/>
+      <c r="G152" s="45"/>
+      <c r="H152" s="45"/>
+      <c r="I152" s="46"/>
       <c r="J152" s="1"/>
       <c r="K152" s="1"/>
       <c r="L152" s="1"/>
@@ -6774,7 +6742,214 @@
       <c r="I997" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="235">
+  <mergeCells count="231">
+    <mergeCell ref="C150:I150"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="F116:G116"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H115:H119"/>
+    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="F103:G103"/>
+    <mergeCell ref="F108:G108"/>
+    <mergeCell ref="C149:I149"/>
+    <mergeCell ref="B134:I134"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="H41:H46"/>
+    <mergeCell ref="H34:H39"/>
+    <mergeCell ref="B120:I120"/>
+    <mergeCell ref="F122:G122"/>
+    <mergeCell ref="C135:I139"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="C147:I147"/>
+    <mergeCell ref="B146:I146"/>
+    <mergeCell ref="C125:D125"/>
+    <mergeCell ref="E41:E46"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="A20:A26"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F118:G118"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="F52:G53"/>
+    <mergeCell ref="A88:A93"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="E55:E60"/>
+    <mergeCell ref="E13:E18"/>
+    <mergeCell ref="F17:I18"/>
+    <mergeCell ref="A13:A19"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="H94:H99"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="I94:I96"/>
+    <mergeCell ref="F38:G39"/>
+    <mergeCell ref="F83:G83"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="F105:G106"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="H121:H126"/>
+    <mergeCell ref="F20:F23"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="E94:E99"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="H76:H80"/>
+    <mergeCell ref="F101:G101"/>
+    <mergeCell ref="F110:G110"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A115:A120"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="H62:H67"/>
+    <mergeCell ref="A41:A47"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C152:I152"/>
+    <mergeCell ref="I62:I65"/>
+    <mergeCell ref="A62:A68"/>
+    <mergeCell ref="F109:G109"/>
+    <mergeCell ref="A34:A40"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="E21:E25"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="B87:I87"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="I82:I85"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="C48:C51"/>
+    <mergeCell ref="A128:A134"/>
+    <mergeCell ref="F59:G60"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="B140:I140"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="E34:E39"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="B61:I61"/>
+    <mergeCell ref="E27:E32"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="I34:I37"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="F45:G46"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="B114:I114"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="E62:E67"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="I27:I30"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A27:A33"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="F31:G32"/>
+    <mergeCell ref="C105:D106"/>
+    <mergeCell ref="E76:E78"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="B93:I93"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A101:A107"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="F10:I11"/>
+    <mergeCell ref="A55:A61"/>
+    <mergeCell ref="F34:F37"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="F24:I25"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="B100:I100"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="B75:I75"/>
+    <mergeCell ref="I88:I91"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="B74:I74"/>
+    <mergeCell ref="A69:A74"/>
+    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="H27:H32"/>
+    <mergeCell ref="C13:C16"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F115:G115"/>
+    <mergeCell ref="I104:I106"/>
+    <mergeCell ref="E101:E106"/>
+    <mergeCell ref="F102:G102"/>
+    <mergeCell ref="B127:I127"/>
+    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="I48:I51"/>
+    <mergeCell ref="E121:E126"/>
+    <mergeCell ref="B68:I68"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="I69:I72"/>
+    <mergeCell ref="H48:H53"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="I97:I99"/>
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="I108:I111"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="J9:J11"/>
+    <mergeCell ref="H101:H106"/>
+    <mergeCell ref="A94:A100"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="I121:I123"/>
+    <mergeCell ref="A5:A12"/>
+    <mergeCell ref="F119:G119"/>
+    <mergeCell ref="B26:I26"/>
+    <mergeCell ref="A75:A81"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="H82:H85"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I115:I118"/>
+    <mergeCell ref="E115:E119"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="C27:C30"/>
+    <mergeCell ref="I101:I103"/>
+    <mergeCell ref="H13:H16"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C151:I151"/>
+    <mergeCell ref="C141:I144"/>
+    <mergeCell ref="F125:G126"/>
+    <mergeCell ref="F112:G112"/>
+    <mergeCell ref="B81:I81"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="I66:I67"/>
+    <mergeCell ref="A82:A87"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="H55:H60"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="E48:E53"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="A147:A152"/>
+    <mergeCell ref="I124:I126"/>
+    <mergeCell ref="F104:G104"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="H108:H111"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="B107:I107"/>
+    <mergeCell ref="C145:I145"/>
+    <mergeCell ref="A121:A127"/>
     <mergeCell ref="C148:I148"/>
     <mergeCell ref="C69:C72"/>
     <mergeCell ref="F123:G123"/>
@@ -6799,217 +6974,6 @@
     <mergeCell ref="F91:G91"/>
     <mergeCell ref="I55:I58"/>
     <mergeCell ref="A135:A140"/>
-    <mergeCell ref="C151:I151"/>
-    <mergeCell ref="C141:I144"/>
-    <mergeCell ref="F125:G126"/>
-    <mergeCell ref="F112:G112"/>
-    <mergeCell ref="B81:I81"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="I66:I67"/>
-    <mergeCell ref="A82:A87"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="H55:H60"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="E48:E53"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="A147:A152"/>
-    <mergeCell ref="I124:I126"/>
-    <mergeCell ref="F104:G104"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="H108:H111"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="B107:I107"/>
-    <mergeCell ref="C145:I145"/>
-    <mergeCell ref="A121:A127"/>
-    <mergeCell ref="J9:J11"/>
-    <mergeCell ref="H101:H106"/>
-    <mergeCell ref="A94:A100"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="I121:I123"/>
-    <mergeCell ref="A5:A12"/>
-    <mergeCell ref="F119:G119"/>
-    <mergeCell ref="B26:I26"/>
-    <mergeCell ref="A75:A81"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="H82:H85"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I115:I118"/>
-    <mergeCell ref="E115:E119"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="C27:C30"/>
-    <mergeCell ref="I101:I103"/>
-    <mergeCell ref="H13:H16"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F115:G115"/>
-    <mergeCell ref="I104:I106"/>
-    <mergeCell ref="F139:I139"/>
-    <mergeCell ref="E101:E106"/>
-    <mergeCell ref="F102:G102"/>
-    <mergeCell ref="B127:I127"/>
-    <mergeCell ref="B40:I40"/>
-    <mergeCell ref="I48:I51"/>
-    <mergeCell ref="E121:E126"/>
-    <mergeCell ref="B68:I68"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="I69:I72"/>
-    <mergeCell ref="H48:H53"/>
-    <mergeCell ref="C34:C37"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="I97:I99"/>
-    <mergeCell ref="B47:I47"/>
-    <mergeCell ref="I108:I111"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="A55:A61"/>
-    <mergeCell ref="F34:F37"/>
-    <mergeCell ref="C20:C23"/>
-    <mergeCell ref="F24:I25"/>
-    <mergeCell ref="F13:F15"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="B100:I100"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="B75:I75"/>
-    <mergeCell ref="I88:I91"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="B74:I74"/>
-    <mergeCell ref="A69:A74"/>
-    <mergeCell ref="A48:A54"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="H27:H32"/>
-    <mergeCell ref="C13:C16"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="I34:I37"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="F45:G46"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="B114:I114"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="E62:E67"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="I27:I30"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="A27:A33"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="F31:G32"/>
-    <mergeCell ref="C105:D106"/>
-    <mergeCell ref="E76:E78"/>
-    <mergeCell ref="F89:G89"/>
-    <mergeCell ref="B93:I93"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A101:A107"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="F10:I11"/>
-    <mergeCell ref="C152:I152"/>
-    <mergeCell ref="I62:I65"/>
-    <mergeCell ref="A62:A68"/>
-    <mergeCell ref="F109:G109"/>
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="A34:A40"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="E21:E25"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="B87:I87"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="I82:I85"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="C48:C51"/>
-    <mergeCell ref="A128:A134"/>
-    <mergeCell ref="F59:G60"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="B33:I33"/>
-    <mergeCell ref="B140:I140"/>
-    <mergeCell ref="F124:G124"/>
-    <mergeCell ref="E34:E39"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="B61:I61"/>
-    <mergeCell ref="E27:E32"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="I94:I96"/>
-    <mergeCell ref="F38:G39"/>
-    <mergeCell ref="F83:G83"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="F105:G106"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="H121:H126"/>
-    <mergeCell ref="F20:F23"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="E94:E99"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="H76:H80"/>
-    <mergeCell ref="F101:G101"/>
-    <mergeCell ref="F110:G110"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A115:A120"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="H62:H67"/>
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="A20:A26"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F118:G118"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="F52:G53"/>
-    <mergeCell ref="A88:A93"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="E55:E60"/>
-    <mergeCell ref="E13:E18"/>
-    <mergeCell ref="F17:I18"/>
-    <mergeCell ref="A13:A19"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="H94:H99"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="B19:I19"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="C150:I150"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="F116:G116"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H115:H119"/>
-    <mergeCell ref="B54:I54"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="F103:G103"/>
-    <mergeCell ref="F108:G108"/>
-    <mergeCell ref="C149:I149"/>
-    <mergeCell ref="B134:I134"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="H41:H46"/>
-    <mergeCell ref="H34:H39"/>
-    <mergeCell ref="C121:D121"/>
-    <mergeCell ref="B120:I120"/>
-    <mergeCell ref="F122:G122"/>
-    <mergeCell ref="C135:I138"/>
-    <mergeCell ref="F121:G121"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="C147:I147"/>
-    <mergeCell ref="B146:I146"/>
-    <mergeCell ref="C125:D125"/>
-    <mergeCell ref="E41:E46"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
